--- a/master-db/genesis.xlsx
+++ b/master-db/genesis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C33074F-8DB0-4FC6-BEE4-37E564333983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901796ED-1CA0-4949-A394-B0EA437ACC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="44">
   <si>
     <t>제조사</t>
   </si>
@@ -169,6 +169,10 @@
   </si>
   <si>
     <t>고객센터문의</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGM95R</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -769,7 +773,7 @@
         <v>21</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
@@ -795,7 +799,7 @@
         <v>21</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
@@ -1041,5 +1045,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>